--- a/artifacts/contabilidade_parametrizada.xlsx
+++ b/artifacts/contabilidade_parametrizada.xlsx
@@ -7,29 +7,32 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTIDADE" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLANO_CONTAS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAPEAMENTO_CONTAS" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVENTOS" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVENTOS_FISCAIS" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LANCAMENTOS" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARTIDAS" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VINCULO_EVENTO_LCTO" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIARIO" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAZAO" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BALANCETE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAPEAMENTO_DF" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRE" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CENARIOS_TRIBUTARIOS" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_PARAM" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_RESULTADOS_OPERACAO" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_APURACAO" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPARATIVO_CENARIOS" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACOES" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVENIENCIA" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTRADAS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPARACAO" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ENTIDADE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLANO_CONTAS" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAPEAMENTO_CONTAS" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVENTOS" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVENTOS_FISCAIS" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LANCAMENTOS" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PARTIDAS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VINCULO_EVENTO_LCTO" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DIARIO" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAZAO" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BALANCETE" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MAPEAMENTO_DF" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BP" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRE" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CENARIOS_TRIBUTARIOS" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_PARAM" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_RESULTADOS_OPERACAO" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_APURACAO" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPARATIVO_CENARIOS" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACOES" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVENIENCIA" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -38,16 +41,41 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="0.0000%"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="&quot;R$&quot; #,##0.00"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="0.0000%"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2933"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <color rgb="0052606D"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F2933"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00323F4B"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -58,7 +86,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -67,16 +95,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00F2F4F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -84,21 +117,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <bottom style="hair">
+        <color rgb="00D9E2EC"/>
+      </bottom>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -834,115 +898,1860 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="005B9BD5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="96" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Workbook contábil parametrizado</t>
-        </is>
-      </c>
+          <t>RESUMO</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Versão</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>spec_11_excel_workbook_v1</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Visão executiva do caso contábil e tributário.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Regra operacional</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Editar somente abas de entrada; regenerar pelo Python.</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Entradas</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>CONFIG, ENTIDADE, PLANO_CONTAS, MAPEAMENTO_CONTAS, EVENTOS, EVENTOS_FISCAIS, MAPEAMENTO_DF, CENARIOS_TRIBUTARIOS e FISCAL_PARAM.</t>
-        </is>
-      </c>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>IDENTIFICAÇÃO</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>NAVEGAÇÃO</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>COD_DF</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>PLANO_CONTAS.COD_DF é espelho denormalizado de MAPEAMENTO_DF e é sobrescrito na regeneração.</t>
-        </is>
-      </c>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>ENT_CBS_2026</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Entradas editáveis</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Tributário</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Spec 08 materializa a interface tributária; Spec 09 calcula CBS 2026; Spec 10 executa múltiplos cenários; Spec 11 compara e materializa saídas fiscais derivadas.</t>
-        </is>
-      </c>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 a 2026-08-31</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Comparação de cenários</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Derivadas</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>LANCAMENTOS, PARTIDAS, VINCULO_EVENTO_LCTO, DIARIO, RAZAO, BALANCETE, BP, DRE, FISCAL_RESULTADOS_OPERACAO, FISCAL_APURACAO, COMPARATIVO_CENARIOS, VALIDACOES e PROVENIENCIA.</t>
-        </is>
-      </c>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Moeda</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Balanço patrimonial</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Fonte de verdade</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Objetos derivados são reconstruídos a partir das abas de entrada.</t>
-        </is>
-      </c>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Cenário baseline</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CBS_2026_BASE</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Demonstração do resultado</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Número de cenários ativos</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Apuração fiscal</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>OPERAÇÕES DO PERÍODO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>RESULTADO CONTÁBIL</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>Operação</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Receita</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Compra de mercadoria à vista</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>CMV</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="F14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Venda a prazo</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Resultado do período</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Aporte de capital</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Ativo final</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Passivo</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Patrimônio líquido</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n"/>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="n"/>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>RESULTADO TRIBUTÁRIO - BASELINE</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>NOTA SOBRE O CENÁRIO-CONTROLE</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Tributo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>CBS</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>O cenário CBS_2026_CONTROLE é um controle estrutural usado para validar a comparação multi-cenário. Ele não representa uma legislação ou regime tributário alternativo.</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Débitos</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Créditos</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
+      <c r="E26" s="2" t="n"/>
+      <c r="F26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>CBS apurada</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>CBS a recolher</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
+      <c r="E28" s="2" t="n"/>
+      <c r="F28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Saldo credor</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Impacto em caixa</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>não calculado</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n"/>
+      <c r="D30" s="2" t="n"/>
+      <c r="E30" s="2" t="n"/>
+      <c r="F30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Impacto em DRE</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>não calculado</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="9">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D24:F27"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="A12:B12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D9" r:id="rId5"/>
+  </hyperlinks>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ID_EVENTO</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>ATRIBUTO_FISCAL</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>VALOR</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>TIPO_VALOR</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>ORIGEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MODELO_DFE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CHAVE_NFE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11111111111111111111111111111111111111111111</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROTOCOLO_AUTORIZACAO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>135260000000001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>STATUS_DFE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>autorizado_nao_cancelado</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>DT_FORNECIMENTO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AMBITO_OPERACAO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>domestica</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>QTD_ITENS_DFE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CST_IBS_CBS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CCLASSTRIB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>VBC_CENTS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PCBS_PERCENT</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>VCBS_CENTS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>DESTINACAO_AQUISICAO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>revenda</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MODELO_DFE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CHAVE_NFE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>22222222222222222222222222222222222222222222</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PROTOCOLO_AUTORIZACAO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>135260000000002</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>STATUS_DFE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>autorizado_nao_cancelado</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>DT_FORNECIMENTO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AMBITO_OPERACAO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>domestica</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>QTD_ITENS_DFE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CST_IBS_CBS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>000</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CCLASSTRIB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>000001</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>VBC_CENTS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>200000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PCBS_PERCENT</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>VCBS_CENTS</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>sintética</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"str,int,decimal,bool,date"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"observada,sintética,template,ajustada"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>NUM_LCTO</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>DT_LCTO</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>VL_LCTO</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>IND_LCTO</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>DT_LCTO_EXT</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>ID_GERACAO</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>VERSAO_REGRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>L000001</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="n">
+        <v>46237</v>
+      </c>
+      <c r="C2" s="12" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="n"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CANONICAL_CBS_2026</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>posting_rules_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>L000002</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C3" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CANONICAL_CBS_2026</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>posting_rules_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>L000003</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CANONICAL_CBS_2026</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>posting_rules_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>L000004</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n">
+        <v>46246</v>
+      </c>
+      <c r="C5" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CANONICAL_CBS_2026</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>posting_rules_v1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>ID_PARTIDA</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>NUM_LCTO</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>COD_CTA</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>COD_CCUS</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>VL_DC</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>IND_DC</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>NUM_ARQ</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>COD_HIST_PAD</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>HIST</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>COD_PART</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>ID_ORIGEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>P000001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L000001</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1.1.03.01</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>NFe-001</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Compra para revenda</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>FORN001</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>P000002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>L000001</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1.1.01.01</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="n">
+        <v>1010</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>NFe-001</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Compra para revenda</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>FORN001</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>E001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>P000003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>L000002</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1.1.02.01</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>NFe-002</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Venda tributada integralmente</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>CLI001</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>P000004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>L000002</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.1.01.01</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>NFe-002</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Venda tributada integralmente</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>CLI001</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>P000005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L000003</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.2.01.01</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>NFe-002</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>CMV - Venda tributada integralmente</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>CLI001</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>P000006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>L000003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.1.03.01</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NFe-002</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>CMV - Venda tributada integralmente</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>CLI001</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>E002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>P000007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>L000004</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.1.01.01</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>CAP-001</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Integralizacao de capital</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>P000008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L000004</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.1.01.01</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>CAP-001</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Integralizacao de capital</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>E003</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -955,17 +2764,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>ID_EVENTO</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>NUM_LCTO</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>ORDEM_LCTO_EVENTO</t>
         </is>
@@ -1039,9 +2848,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1061,59 +2871,59 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>DT_LCTO</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>NUM_LCTO</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>ID_PARTIDA</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>COD_CTA</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>CTA</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>IND_DC</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>VL_DC</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>HIST</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>COD_PART</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>ID_ORIGEM</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -1141,7 +2951,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="12" t="n">
         <v>1010</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -1161,7 +2971,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -1189,7 +2999,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="12" t="n">
         <v>1010</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -1209,7 +3019,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -1237,7 +3047,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="12" t="n">
         <v>2000</v>
       </c>
       <c r="H4" t="inlineStr">
@@ -1257,7 +3067,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -1285,7 +3095,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="12" t="n">
         <v>2000</v>
       </c>
       <c r="H5" t="inlineStr">
@@ -1305,7 +3115,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -1333,7 +3143,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="inlineStr">
@@ -1353,7 +3163,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -1381,7 +3191,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="inlineStr">
@@ -1401,7 +3211,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="11" t="n">
         <v>46246</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1429,7 +3239,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="12" t="n">
         <v>5000</v>
       </c>
       <c r="H8" t="inlineStr">
@@ -1444,7 +3254,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="11" t="n">
         <v>46246</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1472,7 +3282,7 @@
           <t>C</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="12" t="n">
         <v>5000</v>
       </c>
       <c r="H9" t="inlineStr">
@@ -1494,9 +3304,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1519,67 +3330,67 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>COD_CTA</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>CTA</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>DT_LCTO</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>NUM_LCTO</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>ID_PARTIDA</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>DEBITO</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>CREDITO</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>MOVIMENTO_ASSINADO</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>SALDO_ASSINADO</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>SALDO_ABS</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>IND_DC_SALDO</t>
         </is>
       </c>
-      <c r="L1" s="5" t="inlineStr">
+      <c r="L1" s="13" t="inlineStr">
         <is>
           <t>HIST</t>
         </is>
       </c>
-      <c r="M1" s="5" t="inlineStr">
+      <c r="M1" s="13" t="inlineStr">
         <is>
           <t>ID_ORIGEM</t>
         </is>
@@ -1596,7 +3407,7 @@
           <t>Caixa</t>
         </is>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -1609,19 +3420,19 @@
           <t>P000002</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="12" t="n">
         <v>1010</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="12" t="n">
         <v>-1010</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="12" t="n">
         <v>-1010</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="12" t="n">
         <v>1010</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -1651,7 +3462,7 @@
           <t>Caixa</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="11" t="n">
         <v>46246</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -1664,19 +3475,19 @@
           <t>P000007</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="12" t="n">
         <v>3990</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="12" t="n">
         <v>3990</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -1706,7 +3517,7 @@
           <t>Clientes</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -1719,19 +3530,19 @@
           <t>P000003</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="12" t="n">
         <v>2000</v>
       </c>
       <c r="K4" t="inlineStr">
@@ -1761,7 +3572,7 @@
           <t>Mercadorias para Revenda</t>
         </is>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="C5" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -1774,19 +3585,19 @@
           <t>P000001</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="12" t="n">
         <v>1010</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="12" t="n">
         <v>1010</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="12" t="n">
         <v>1010</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="12" t="n">
         <v>1010</v>
       </c>
       <c r="K5" t="inlineStr">
@@ -1816,7 +3627,7 @@
           <t>Mercadorias para Revenda</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C6" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1829,19 +3640,19 @@
           <t>P000006</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="12" t="n">
         <v>-1000</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -1871,7 +3682,7 @@
           <t>Capital Social Integralizado</t>
         </is>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="11" t="n">
         <v>46246</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1884,19 +3695,19 @@
           <t>P000008</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="12" t="n">
         <v>-5000</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="12" t="n">
         <v>-5000</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="12" t="n">
         <v>5000</v>
       </c>
       <c r="K7" t="inlineStr">
@@ -1926,7 +3737,7 @@
           <t>Receita de Vendas</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -1939,19 +3750,19 @@
           <t>P000004</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="12" t="n">
         <v>-2000</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="12" t="n">
         <v>-2000</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="12" t="n">
         <v>2000</v>
       </c>
       <c r="K8" t="inlineStr">
@@ -1981,7 +3792,7 @@
           <t>Custo das Mercadorias Vendidas</t>
         </is>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="C9" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -1994,19 +3805,19 @@
           <t>P000005</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="K9" t="inlineStr">
@@ -2033,9 +3844,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2055,62 +3867,62 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>DT_INI</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>DT_FIN</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>COD_CTA</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>COD_CCUS</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>VL_SLD_INI</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>IND_DC_INI</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>VL_DEB</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>VL_CRED</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>VL_SLD_FIN</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>IND_DC_FIN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -2118,7 +3930,7 @@
           <t>1.1.01.01</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -2126,13 +3938,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="12" t="n">
         <v>1010</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="12" t="n">
         <v>3990</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -2142,10 +3954,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -2153,7 +3965,7 @@
           <t>1.1.01.02</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -2161,13 +3973,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -2177,10 +3989,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -2188,7 +4000,7 @@
           <t>1.1.02.01</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
@@ -2196,13 +4008,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="12" t="n">
         <v>2000</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -2212,10 +4024,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C5" t="inlineStr">
@@ -2223,7 +4035,7 @@
           <t>1.1.03.01</t>
         </is>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
@@ -2231,13 +4043,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="12" t="n">
         <v>1010</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -2247,10 +4059,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C6" t="inlineStr">
@@ -2258,7 +4070,7 @@
           <t>1.1.04.01</t>
         </is>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
@@ -2266,13 +4078,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -2282,10 +4094,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C7" t="inlineStr">
@@ -2293,7 +4105,7 @@
           <t>1.2.01.01</t>
         </is>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
@@ -2301,13 +4113,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -2317,10 +4129,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -2328,7 +4140,7 @@
           <t>1.2.01.02</t>
         </is>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
@@ -2336,13 +4148,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -2352,10 +4164,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -2363,7 +4175,7 @@
           <t>2.1.01.01</t>
         </is>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
@@ -2371,13 +4183,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -2387,10 +4199,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C10" t="inlineStr">
@@ -2398,7 +4210,7 @@
           <t>2.1.02.01</t>
         </is>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
@@ -2406,13 +4218,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -2422,10 +4234,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C11" t="inlineStr">
@@ -2433,7 +4245,7 @@
           <t>2.1.03.01</t>
         </is>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="inlineStr">
@@ -2441,13 +4253,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
@@ -2457,10 +4269,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -2468,7 +4280,7 @@
           <t>2.2.01.01</t>
         </is>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
@@ -2476,13 +4288,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
@@ -2492,10 +4304,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B13" s="3" t="n">
+      <c r="B13" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C13" t="inlineStr">
@@ -2503,7 +4315,7 @@
           <t>3.1.01.01</t>
         </is>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
@@ -2511,13 +4323,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="12" t="n">
         <v>5000</v>
       </c>
       <c r="J13" t="inlineStr">
@@ -2527,10 +4339,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B14" s="3" t="n">
+      <c r="B14" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C14" t="inlineStr">
@@ -2538,7 +4350,7 @@
           <t>3.2.01.01</t>
         </is>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
@@ -2546,13 +4358,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
@@ -2562,10 +4374,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B15" s="3" t="n">
+      <c r="B15" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C15" t="inlineStr">
@@ -2573,7 +4385,7 @@
           <t>4.1.01.01</t>
         </is>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
@@ -2581,13 +4393,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="12" t="n">
         <v>2000</v>
       </c>
       <c r="J15" t="inlineStr">
@@ -2597,10 +4409,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B16" s="3" t="n">
+      <c r="B16" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -2608,7 +4420,7 @@
           <t>4.2.01.01</t>
         </is>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
@@ -2616,13 +4428,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="J16" t="inlineStr">
@@ -2632,10 +4444,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -2643,7 +4455,7 @@
           <t>4.3.01.01</t>
         </is>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="inlineStr">
@@ -2651,13 +4463,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
@@ -2667,10 +4479,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B18" s="3" t="n">
+      <c r="B18" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C18" t="inlineStr">
@@ -2678,7 +4490,7 @@
           <t>4.3.01.02</t>
         </is>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
@@ -2686,13 +4498,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
@@ -2702,10 +4514,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B19" s="3" t="n">
+      <c r="B19" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C19" t="inlineStr">
@@ -2713,7 +4525,7 @@
           <t>4.3.01.03</t>
         </is>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
@@ -2721,13 +4533,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="inlineStr">
@@ -2737,10 +4549,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B20" s="3" t="n">
+      <c r="B20" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C20" t="inlineStr">
@@ -2748,7 +4560,7 @@
           <t>4.3.01.04</t>
         </is>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
@@ -2756,13 +4568,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="inlineStr">
@@ -2772,10 +4584,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B21" s="3" t="n">
+      <c r="B21" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C21" t="inlineStr">
@@ -2783,7 +4595,7 @@
           <t>4.3.02.01</t>
         </is>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
@@ -2791,13 +4603,13 @@
           <t>D</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
@@ -2814,9 +4626,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2829,17 +4642,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>COD_CTA</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>DEMONSTRACAO</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>COD_LINHA</t>
         </is>
@@ -3198,9 +5011,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3217,44 +5031,44 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>DT_REF</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>ORDEM</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>COD_LINHA</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>NIVEL</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>TIPO_LINHA</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>LINHA</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>VL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B2" t="n">
@@ -3278,12 +5092,12 @@
           <t>Ativo</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="12" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B3" t="n">
@@ -3307,12 +5121,12 @@
           <t>Ativo Circulante</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="12" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B4" t="n">
@@ -3336,12 +5150,12 @@
           <t>Caixa</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="12" t="n">
         <v>3990</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B5" t="n">
@@ -3365,12 +5179,12 @@
           <t>Bancos Conta Movimento</t>
         </is>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B6" t="n">
@@ -3394,12 +5208,12 @@
           <t>Clientes</t>
         </is>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="12" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B7" t="n">
@@ -3423,12 +5237,12 @@
           <t>Estoques</t>
         </is>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="12" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B8" t="n">
@@ -3452,12 +5266,12 @@
           <t>Tributos a Recuperar</t>
         </is>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B9" t="n">
@@ -3481,12 +5295,12 @@
           <t>Ativo Não Circulante</t>
         </is>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B10" t="n">
@@ -3510,12 +5324,12 @@
           <t>Imobilizado</t>
         </is>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B11" t="n">
@@ -3539,12 +5353,12 @@
           <t>(-) Depreciação Acumulada</t>
         </is>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B12" t="n">
@@ -3568,12 +5382,12 @@
           <t>Passivo</t>
         </is>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B13" t="n">
@@ -3597,12 +5411,12 @@
           <t>Passivo Circulante</t>
         </is>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B14" t="n">
@@ -3626,12 +5440,12 @@
           <t>Fornecedores</t>
         </is>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B15" t="n">
@@ -3655,12 +5469,12 @@
           <t>Obrigações Trabalhistas</t>
         </is>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B16" t="n">
@@ -3684,12 +5498,12 @@
           <t>Obrigações Tributárias</t>
         </is>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B17" t="n">
@@ -3713,12 +5527,12 @@
           <t>Passivo Não Circulante</t>
         </is>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B18" t="n">
@@ -3742,12 +5556,12 @@
           <t>Empréstimos e Financiamentos</t>
         </is>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B19" t="n">
@@ -3771,12 +5585,12 @@
           <t>Patrimônio Líquido</t>
         </is>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="12" t="n">
         <v>6000</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B20" t="n">
@@ -3800,12 +5614,12 @@
           <t>Capital Social</t>
         </is>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="12" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B21" t="n">
@@ -3829,12 +5643,12 @@
           <t>Resultados Acumulados</t>
         </is>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B22" t="n">
@@ -3858,12 +5672,12 @@
           <t>Resultado do Período</t>
         </is>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="12" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="B23" t="n">
@@ -3887,7 +5701,7 @@
           <t>Total do Passivo e Patrimônio Líquido</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="12" t="n">
         <v>6000</v>
       </c>
     </row>
@@ -3899,9 +5713,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A5A5A5"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -3919,52 +5734,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>DT_INI</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>DT_FIN</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>ORDEM</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>COD_LINHA</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>NIVEL</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>TIPO_LINHA</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>LINHA</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>VL</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C2" t="n">
@@ -3988,15 +5803,15 @@
           <t>Receita de Vendas</t>
         </is>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="12" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C3" t="n">
@@ -4020,15 +5835,15 @@
           <t>Receita Líquida</t>
         </is>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="12" t="n">
         <v>2000</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C4" t="n">
@@ -4052,15 +5867,15 @@
           <t>(-) Custo das Mercadorias Vendidas</t>
         </is>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="12" t="n">
         <v>-1000</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B5" s="3" t="n">
+      <c r="B5" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C5" t="n">
@@ -4084,15 +5899,15 @@
           <t>Resultado Bruto</t>
         </is>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="12" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B6" s="3" t="n">
+      <c r="B6" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C6" t="n">
@@ -4116,15 +5931,15 @@
           <t>(-) Salários e Encargos</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C7" t="n">
@@ -4148,15 +5963,15 @@
           <t>(-) Aluguéis</t>
         </is>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C8" t="n">
@@ -4180,15 +5995,15 @@
           <t>(-) Energia e Utilidades</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B9" s="3" t="n">
+      <c r="B9" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C9" t="n">
@@ -4212,15 +6027,15 @@
           <t>(-) Depreciação</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B10" s="3" t="n">
+      <c r="B10" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C10" t="n">
@@ -4244,15 +6059,15 @@
           <t>Despesas Operacionais</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B11" s="3" t="n">
+      <c r="B11" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C11" t="n">
@@ -4276,15 +6091,15 @@
           <t>(-) Despesas Financeiras</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="11" t="n">
         <v>46235</v>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B12" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="C12" t="n">
@@ -4308,7 +6123,7 @@
           <t>Resultado do Período</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="12" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -4320,9 +6135,469 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="005B9BD5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ENTRADAS</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Mapa das abas que podem ser alteradas antes da regeneração pelo Python.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ENTRADAS DE USO COMUM</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ORDEM</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>O_QUE_CONTEM</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>QUANDO_EDITAR</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>NIVEL_DE_CUIDADO</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>período e configuração geral</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>alterar período/simulação</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>baixo</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>ENTIDADE</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>atributos da empresa</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>alterar características factuais da entidade</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>médio</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>EVENTOS</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>operações econômicas</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>alterar fatos econômicos</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>EVENTOS_FISCAIS</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>atributos fiscais dos eventos</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>alterar dados documentais/fiscais</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>CONFIGURAÇÕES ESTRUTURAIS</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>ORDEM</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>O_QUE_CONTEM</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>QUANDO_EDITAR</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>NIVEL_DE_CUIDADO</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>PLANO_CONTAS</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>plano de contas auditável</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>ajustar estrutura contábil</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>MAPEAMENTO_CONTAS</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>papéis contábeis para contas</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>recodificar contas sem mudar regras econômicas</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>MAPEAMENTO_DF</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>contas para linhas de BP/DRE</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>alterar apresentação das demonstrações</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n"/>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>PARÂMETROS NORMATIVOS - ALTA SENSIBILIDADE</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>ORDEM</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>O_QUE_CONTEM</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>QUANDO_EDITAR</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>NIVEL_DE_CUIDADO</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>CENARIOS_TRIBUTARIOS</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>cenários e regimes tributários</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>configurar cenários contrafactuais</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>FISCAL_PARAM</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>parâmetros normativos versionados</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>somente com base normativa rastreável</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>muito alto</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A19:E19"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId9"/>
+  </hyperlinks>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4343,57 +6618,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID_CENARIO</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>ID_ENTIDADE</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>DESCRICAO</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>E_BASELINE</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>DT_REFERENCIA_NORMATIVA</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>REGIME_ENTIDADE</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>REGIME_IR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>REGIME_CONSUMO</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>REGIME_ESPECIAL</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>ID_VERSAO_NORMATIVA</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>ATIVO</t>
         </is>
@@ -4418,7 +6693,7 @@
       <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="F2" t="inlineStr">
@@ -4461,7 +6736,7 @@
       <c r="D3" t="b">
         <v>0</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="E3" s="11" t="n">
         <v>46265</v>
       </c>
       <c r="F3" t="inlineStr">
@@ -4501,9 +6776,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -4529,82 +6805,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID_PARAM</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>ID_VERSAO_NORMATIVA</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>ID_REGRA</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>TRIBUTO</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>CHAVE_PARAM</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>TIPO_VALOR</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>TIPO_FONTE</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>FONTE_TITULO</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>FONTE_URL</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>DISPOSITIVO</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>VERSAO_NORMA</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>VIG_INI</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>VIG_FIM</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>DATA_CONSULTA</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>VERSAO_REGRA</t>
         </is>
@@ -4671,13 +6947,13 @@
           <t>LC 214/2025 compilada</t>
         </is>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="M2" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="N2" s="11" t="n">
         <v>46387</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="O2" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P2" t="inlineStr">
@@ -4747,11 +7023,11 @@
           <t>Decreto 12.955/2026</t>
         </is>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="n">
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P3" t="inlineStr">
@@ -4821,11 +7097,11 @@
           <t>Ato Conjunto RFB CGIBS 01/2025</t>
         </is>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="n">
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P4" t="inlineStr">
@@ -4895,11 +7171,11 @@
           <t>Ato Conjunto RFB CGIBS 04/2026</t>
         </is>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="11" t="n">
         <v>46237</v>
       </c>
-      <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="n">
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P5" t="inlineStr">
@@ -4969,11 +7245,11 @@
           <t>Tabela CST IBS CBS 2026-06-23</t>
         </is>
       </c>
-      <c r="M6" s="3" t="n">
+      <c r="M6" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n">
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P6" t="inlineStr">
@@ -5043,11 +7319,11 @@
           <t>Tabela cClassTrib IBS CBS 2026-06-23</t>
         </is>
       </c>
-      <c r="M7" s="3" t="n">
+      <c r="M7" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="n">
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P7" t="inlineStr">
@@ -5117,11 +7393,11 @@
           <t>NF-e Nota Tecnica 2025.002 v1.51</t>
         </is>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N8" s="3" t="n"/>
-      <c r="O8" s="3" t="n">
+      <c r="N8" s="11" t="n"/>
+      <c r="O8" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P8" t="inlineStr">
@@ -5191,11 +7467,11 @@
           <t>LC 214/2025 compilada</t>
         </is>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n">
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P9" t="inlineStr">
@@ -5265,13 +7541,13 @@
           <t>Ato Conjunto RFB/CGIBS 02/2026 + rol oficial CGIBS</t>
         </is>
       </c>
-      <c r="M10" s="3" t="n">
+      <c r="M10" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N10" s="3" t="n">
+      <c r="N10" s="11" t="n">
         <v>46265</v>
       </c>
-      <c r="O10" s="3" t="n">
+      <c r="O10" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P10" t="inlineStr">
@@ -5341,13 +7617,13 @@
           <t>Manual RTC Projeto Piloto v1 13/01/2026 + rol oficial CGIBS</t>
         </is>
       </c>
-      <c r="M11" s="3" t="n">
+      <c r="M11" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N11" s="3" t="n">
+      <c r="N11" s="11" t="n">
         <v>46265</v>
       </c>
-      <c r="O11" s="3" t="n">
+      <c r="O11" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P11" t="inlineStr">
@@ -5417,13 +7693,13 @@
           <t>Decreto 12.955/2026</t>
         </is>
       </c>
-      <c r="M12" s="3" t="n">
+      <c r="M12" s="11" t="n">
         <v>46023</v>
       </c>
-      <c r="N12" s="3" t="n">
+      <c r="N12" s="11" t="n">
         <v>46387</v>
       </c>
-      <c r="O12" s="3" t="n">
+      <c r="O12" s="11" t="n">
         <v>46267</v>
       </c>
       <c r="P12" t="inlineStr">
@@ -5448,9 +7724,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5469,47 +7746,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>ID_CENARIO</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>ID_EVENTO</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>TRIBUTO</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>INCIDE</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>ALIQUOTA</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>CREDITO</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>DEBITO</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>VERSAO_REGRA</t>
         </is>
@@ -5534,16 +7811,16 @@
       <c r="D2" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="F2" s="6" t="n">
+      <c r="F2" s="14" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
@@ -5571,16 +7848,16 @@
       <c r="D3" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="F3" s="6" t="n">
+      <c r="F3" s="14" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I3" t="inlineStr">
@@ -5608,16 +7885,16 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="12" t="n">
         <v>1000</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="F4" s="14" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
@@ -5645,16 +7922,16 @@
       <c r="D5" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="14" t="n">
         <v>0.008999999999999999</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I5" t="inlineStr">
@@ -5671,125 +7948,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>CHAVE</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>VALOR</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>simulation_id</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CANONICAL_CBS_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>start_date</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>46235</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>end_date</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BRL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>seed</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>scenario_name</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>cbs_2026_counterfactual_control</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>spec_version</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>spec_11_excel_workbook_v1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"BRL"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5807,42 +7969,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>ID_CENARIO</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>TRIBUTO</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>S_APUR</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>T_RECOLHER</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>P_CASH</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>E_DRE</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>C_SALDO</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>VERSAO_REGRA</t>
         </is>
@@ -5859,15 +8021,15 @@
           <t>CBS</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n">
+      <c r="E2" s="12" t="n"/>
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
@@ -5887,15 +8049,15 @@
           <t>CBS</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="4" t="n"/>
-      <c r="F3" s="4" t="n"/>
-      <c r="G3" s="4" t="n">
+      <c r="E3" s="12" t="n"/>
+      <c r="F3" s="12" t="n"/>
+      <c r="G3" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
@@ -5912,9 +8074,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5932,42 +8095,42 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>ID_CENARIO_BASE</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>ID_CENARIO</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>TRIBUTO</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>DELTA_S_APUR</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>DELTA_T_RECOLHER</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>DELTA_P_CASH</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>DELTA_E_DRE</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>DELTA_C_SALDO</t>
         </is>
@@ -5989,15 +8152,15 @@
           <t>CBS</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n">
+      <c r="F2" s="12" t="n"/>
+      <c r="G2" s="12" t="n"/>
+      <c r="H2" s="12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6009,9 +8172,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008064A2"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6032,57 +8196,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>ETAPA</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="13" t="inlineStr">
         <is>
           <t>ISSUE_CODE</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="13" t="inlineStr">
         <is>
           <t>MENSAGEM</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="13" t="inlineStr">
         <is>
           <t>ACCOUNT_CODE</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="13" t="inlineStr">
         <is>
           <t>EVENT_ID</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="13" t="inlineStr">
         <is>
           <t>ENTRY_ID</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="13" t="inlineStr">
         <is>
           <t>POSTING_ID</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="13" t="inlineStr">
         <is>
           <t>ENTITY_ID</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="13" t="inlineStr">
         <is>
           <t>SCENARIO_ID</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="13" t="inlineStr">
         <is>
           <t>TAX_PARAM_ID</t>
         </is>
@@ -6276,9 +8440,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="008064A2"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6290,12 +8455,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>CHAVE</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="13" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
@@ -6480,6 +8645,570 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="005B9BD5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>COMPARAÇÃO</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Leitura descritiva do baseline contra o cenário alternativo.</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Cenário baseline</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CBS_2026_BASE</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Apuração técnica</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Cenário alternativo</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CBS_2026_CONTROLE</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Comparativo técnico</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Tributo</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CBS</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Cenários tributários</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n"/>
+      <c r="B7" s="2" t="n"/>
+      <c r="C7" s="2" t="n"/>
+      <c r="D7" s="2" t="n"/>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>INDICADOR</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>ALTERNATIVO</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>DELTA</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Saldo apurado</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="2" t="n"/>
+      <c r="F10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Valor a recolher</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="2" t="n"/>
+      <c r="F11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Saldo credor</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Impacto em caixa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>não calculado</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>não calculado</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>não calculado</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Impacto em DRE</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>não calculado</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>não calculado</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>não calculado</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n"/>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
+      <c r="E15" s="2" t="n"/>
+      <c r="F15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n"/>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="n"/>
+      <c r="F16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>NOTA</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Os deltas atuais são nulos porque o cenário alternativo é apenas um controle estrutural. Uma comparação econômica substantiva exige um segundo tratamento tributário juridicamente especificado.</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n"/>
+      <c r="E18" s="2" t="n"/>
+      <c r="F18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
+      <c r="E20" s="2" t="n"/>
+      <c r="F20" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A18:D20"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D4" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D6" r:id="rId3"/>
+  </hyperlinks>
+  <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="005B9BD5"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Workbook contábil parametrizado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Versão</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>spec_11_excel_workbook_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Como começar</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Comece por RESUMO. Use ENTRADAS para localizar o que pode ser editado. Use COMPARACAO para analisar resultados entre cenários.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regra operacional</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Editar somente abas de entrada; regenerar pelo Python. As demais abas fornecem detalhamento e auditoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Entradas</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CONFIG, ENTIDADE, PLANO_CONTAS, MAPEAMENTO_CONTAS, EVENTOS, EVENTOS_FISCAIS, MAPEAMENTO_DF, CENARIOS_TRIBUTARIOS e FISCAL_PARAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>COD_DF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PLANO_CONTAS.COD_DF é espelho denormalizado de MAPEAMENTO_DF e é sobrescrito na regeneração.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tributário</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Spec 08 materializa a interface tributária; Spec 09 calcula CBS 2026; Spec 10 executa múltiplos cenários; Spec 11 compara e materializa saídas fiscais derivadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Derivadas</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LANCAMENTOS, PARTIDAS, VINCULO_EVENTO_LCTO, DIARIO, RAZAO, BALANCETE, BP, DRE, FISCAL_RESULTADOS_OPERACAO, FISCAL_APURACAO, COMPARATIVO_CENARIOS, VALIDACOES e PROVENIENCIA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fonte de verdade</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Objetos derivados são reconstruídos a partir das abas de entrada.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>CHAVE</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>VALOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>simulation_id</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CANONICAL_CBS_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="n">
+        <v>46235</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n">
+        <v>46265</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>seed</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>scenario_name</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>cbs_2026_counterfactual_control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>spec_version</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>spec_11_excel_workbook_v1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"BRL"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6494,27 +9223,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID_ENTIDADE</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>ATRIBUTO</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>VALOR</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>TIPO_VALOR</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>ORIGEM</t>
         </is>
@@ -6644,9 +9373,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -6667,64 +9397,64 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>DT_ALT</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>COD_NAT</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>IND_CTA</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>NIVEL</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>COD_CTA</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>COD_CTA_SUP</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>CTA</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>NAT_SALDO_NORMAL</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>COD_DF</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>ATIVA</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>ORIGEM</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -6765,7 +9495,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -6811,7 +9541,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -6857,7 +9587,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -6908,7 +9638,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -6959,7 +9689,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -7005,7 +9735,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -7056,7 +9786,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -7102,7 +9832,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -7153,7 +9883,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -7199,7 +9929,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -7250,7 +9980,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -7296,7 +10026,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -7342,7 +10072,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -7393,7 +10123,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -7444,7 +10174,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -7485,7 +10215,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -7531,7 +10261,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -7577,7 +10307,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -7628,7 +10358,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -7674,7 +10404,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -7725,7 +10455,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -7771,7 +10501,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -7822,7 +10552,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -7868,7 +10598,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -7914,7 +10644,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -7965,7 +10695,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -8006,7 +10736,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -8052,7 +10782,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -8098,7 +10828,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -8149,7 +10879,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -8195,7 +10925,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -8241,7 +10971,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -8292,7 +11022,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -8333,7 +11063,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -8379,7 +11109,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -8425,7 +11155,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -8476,7 +11206,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -8522,7 +11252,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -8568,7 +11298,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -8619,7 +11349,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -8665,7 +11395,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -8711,7 +11441,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -8762,7 +11492,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -8813,7 +11543,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -8864,7 +11594,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -8915,7 +11645,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -8961,7 +11691,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="11" t="n">
         <v>46235</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -9036,9 +11766,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9050,12 +11781,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>PAPEL_CONTABIL</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>COD_CTA</t>
         </is>
@@ -9249,9 +11980,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9277,82 +12009,82 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>ID_EVENTO</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>DT_EVENTO</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>CLASSE_EVENTO</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>TIPO_EVENTO</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>DIRECAO</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>NATUREZA</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>VL_EVENTO</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>VL_CUSTO</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>MEIO_FINANCEIRO</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>CATEGORIA_DESPESA</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>COD_PART</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>COND_PAGTO</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>DOC_REF</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>HIST</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>ORIGEM</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>SPEC_VERSION</t>
         </is>
@@ -9364,7 +12096,7 @@
           <t>E001</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n">
+      <c r="B2" s="11" t="n">
         <v>46237</v>
       </c>
       <c r="C2" t="inlineStr">
@@ -9387,10 +12119,10 @@
           <t>bem</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="12" t="n">
         <v>1010</v>
       </c>
-      <c r="H2" s="4" t="n"/>
+      <c r="H2" s="12" t="n"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>caixa</t>
@@ -9433,7 +12165,7 @@
           <t>E002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n">
+      <c r="B3" s="11" t="n">
         <v>46244</v>
       </c>
       <c r="C3" t="inlineStr">
@@ -9456,10 +12188,10 @@
           <t>bem</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="12" t="n">
         <v>2000</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="12" t="n">
         <v>1000</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -9499,7 +12231,7 @@
           <t>E003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="11" t="n">
         <v>46246</v>
       </c>
       <c r="C4" t="inlineStr">
@@ -9522,10 +12254,10 @@
           <t>financeiro</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="12" t="n">
         <v>5000</v>
       </c>
-      <c r="H4" s="4" t="n"/>
+      <c r="H4" s="12" t="n"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>caixa</t>
@@ -9589,1354 +12321,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>ID_EVENTO</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>ATRIBUTO_FISCAL</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>VALOR</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>TIPO_VALOR</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>ORIGEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>MODELO_DFE</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CHAVE_NFE</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>11111111111111111111111111111111111111111111</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>PROTOCOLO_AUTORIZACAO</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>135260000000001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>STATUS_DFE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>autorizado_nao_cancelado</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>DT_FORNECIMENTO</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-08-03</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>AMBITO_OPERACAO</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>domestica</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>QTD_ITENS_DFE</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CST_IBS_CBS</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CCLASSTRIB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>000001</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>VBC_CENTS</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>PCBS_PERCENT</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>VCBS_CENTS</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>900</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>DESTINACAO_AQUISICAO</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>revenda</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>MODELO_DFE</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CHAVE_NFE</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>22222222222222222222222222222222222222222222</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PROTOCOLO_AUTORIZACAO</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>135260000000002</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>STATUS_DFE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>autorizado_nao_cancelado</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>DT_FORNECIMENTO</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>AMBITO_OPERACAO</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>domestica</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>QTD_ITENS_DFE</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CST_IBS_CBS</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>000</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>CCLASSTRIB</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>000001</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>VBC_CENTS</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>200000</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>PCBS_PERCENT</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>VCBS_CENTS</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1800</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>sintética</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"str,int,decimal,bool,date"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"observada,sintética,template,ajustada"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>NUM_LCTO</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>DT_LCTO</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>VL_LCTO</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>IND_LCTO</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>DT_LCTO_EXT</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>ID_GERACAO</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>VERSAO_REGRA</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>L000001</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>46237</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>1010</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CANONICAL_CBS_2026</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>posting_rules_v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>L000002</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>CANONICAL_CBS_2026</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>posting_rules_v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>L000003</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="n">
-        <v>46244</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="n"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>CANONICAL_CBS_2026</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>posting_rules_v1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>L000004</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>46246</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>CANONICAL_CBS_2026</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>posting_rules_v1</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="42" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>ID_PARTIDA</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>NUM_LCTO</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>COD_CTA</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>COD_CCUS</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>VL_DC</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>IND_DC</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>NUM_ARQ</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>COD_HIST_PAD</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>HIST</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>COD_PART</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>ID_ORIGEM</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>P000001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>L000001</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1.1.03.01</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>NFe-001</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Compra para revenda</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>FORN001</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>P000002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>L000001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1.1.01.01</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>1010</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>NFe-001</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Compra para revenda</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>FORN001</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>E001</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>P000003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>L000002</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1.1.02.01</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>NFe-002</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Venda tributada integralmente</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>CLI001</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>P000004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>L000002</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.1.01.01</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>NFe-002</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Venda tributada integralmente</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>CLI001</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>P000005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>L000003</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.2.01.01</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>NFe-002</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CMV - Venda tributada integralmente</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>CLI001</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>P000006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>L000003</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1.1.03.01</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>NFe-002</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CMV - Venda tributada integralmente</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>CLI001</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>E002</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P000007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>L000004</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1.1.01.01</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>CAP-001</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Integralizacao de capital</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>E003</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P000008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>L000004</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.1.01.01</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>CAP-001</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Integralizacao de capital</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>E003</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>
--- a/artifacts/contabilidade_parametrizada.xlsx
+++ b/artifacts/contabilidade_parametrizada.xlsx
@@ -28,11 +28,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DRE" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CENARIOS_TRIBUTARIOS" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_PARAM" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_RESULTADOS_OPERACAO" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_APURACAO" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPARATIVO_CENARIOS" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACOES" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVENIENCIA" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ANALISE_PARAM" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_RESULTADOS_OPERACAO" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FISCAL_APURACAO" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPARATIVO_CENARIOS" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIMPLES_2027_RESULTADOS" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SIMPLES_2027_COMPARACAO" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACOES" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROVENIENCIA" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -398,7 +401,21 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_FISCAL_RESULTADOS_OPERACAO" displayName="tbl_FISCAL_RESULTADOS_OPERACAO" ref="A1:I5" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_ANALISE_PARAM" displayName="tbl_ANALISE_PARAM" ref="A1:E1" headerRowCount="1">
+  <autoFilter ref="A1:E1"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="ID_ANALISE"/>
+    <tableColumn id="2" name="CHAVE_PARAM"/>
+    <tableColumn id="3" name="VALOR"/>
+    <tableColumn id="4" name="TIPO_VALOR"/>
+    <tableColumn id="5" name="DESCRICAO"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_FISCAL_RESULTADOS_OPERACAO" displayName="tbl_FISCAL_RESULTADOS_OPERACAO" ref="A1:I5" headerRowCount="1">
   <autoFilter ref="A1:I5"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID_CENARIO"/>
@@ -410,23 +427,6 @@
     <tableColumn id="7" name="CREDITO"/>
     <tableColumn id="8" name="DEBITO"/>
     <tableColumn id="9" name="VERSAO_REGRA"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_FISCAL_APURACAO" displayName="tbl_FISCAL_APURACAO" ref="A1:H3" headerRowCount="1">
-  <autoFilter ref="A1:H3"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="ID_CENARIO"/>
-    <tableColumn id="2" name="TRIBUTO"/>
-    <tableColumn id="3" name="S_APUR"/>
-    <tableColumn id="4" name="T_RECOLHER"/>
-    <tableColumn id="5" name="P_CASH"/>
-    <tableColumn id="6" name="E_DRE"/>
-    <tableColumn id="7" name="C_SALDO"/>
-    <tableColumn id="8" name="VERSAO_REGRA"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -447,7 +447,24 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_COMPARATIVO_CENARIOS" displayName="tbl_COMPARATIVO_CENARIOS" ref="A1:H2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_FISCAL_APURACAO" displayName="tbl_FISCAL_APURACAO" ref="A1:H3" headerRowCount="1">
+  <autoFilter ref="A1:H3"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="ID_CENARIO"/>
+    <tableColumn id="2" name="TRIBUTO"/>
+    <tableColumn id="3" name="S_APUR"/>
+    <tableColumn id="4" name="T_RECOLHER"/>
+    <tableColumn id="5" name="P_CASH"/>
+    <tableColumn id="6" name="E_DRE"/>
+    <tableColumn id="7" name="C_SALDO"/>
+    <tableColumn id="8" name="VERSAO_REGRA"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_COMPARATIVO_CENARIOS" displayName="tbl_COMPARATIVO_CENARIOS" ref="A1:H2" headerRowCount="1">
   <autoFilter ref="A1:H2"/>
   <tableColumns count="8">
     <tableColumn id="1" name="ID_CENARIO_BASE"/>
@@ -463,9 +480,62 @@
 </table>
 </file>
 
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_VALIDACOES" displayName="tbl_VALIDACOES" ref="A1:K13" headerRowCount="1">
-  <autoFilter ref="A1:K13"/>
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_SIMPLES_2027_RESULTADOS" displayName="tbl_SIMPLES_2027_RESULTADOS" ref="A1:AA1" headerRowCount="1">
+  <autoFilter ref="A1:AA1"/>
+  <tableColumns count="27">
+    <tableColumn id="1" name="ID_CENARIO"/>
+    <tableColumn id="2" name="REGIME_CONSUMO"/>
+    <tableColumn id="3" name="RECEITA_MES"/>
+    <tableColumn id="4" name="RBT12"/>
+    <tableColumn id="5" name="ALIQUOTA_EFETIVA_SIMPLES"/>
+    <tableColumn id="6" name="DAS_TOTAL"/>
+    <tableColumn id="7" name="DAS_CBS"/>
+    <tableColumn id="8" name="DAS_IBS"/>
+    <tableColumn id="9" name="DAS_OUTROS"/>
+    <tableColumn id="10" name="CBS_REGULAR_RATE_FRACTION"/>
+    <tableColumn id="11" name="CBS_RATE_SOURCE"/>
+    <tableColumn id="12" name="CBS_DEBITO_REGULAR"/>
+    <tableColumn id="13" name="CBS_CREDITO_EMPRESA_POTENCIAL"/>
+    <tableColumn id="14" name="CBS_CREDITO_EMPRESA_MODELADO"/>
+    <tableColumn id="15" name="CBS_VALOR_LIQUIDO_MODELADO"/>
+    <tableColumn id="16" name="CBS_SALDO_CREDOR_MODELADO"/>
+    <tableColumn id="17" name="IBS_REGULAR_RATE_FRACTION"/>
+    <tableColumn id="18" name="IBS_DEBITO_REGULAR"/>
+    <tableColumn id="19" name="IBS_CREDITO_EMPRESA_POTENCIAL"/>
+    <tableColumn id="20" name="IBS_CREDITO_EMPRESA_MODELADO"/>
+    <tableColumn id="21" name="IBS_VALOR_LIQUIDO_MODELADO"/>
+    <tableColumn id="22" name="IBS_SALDO_CREDOR_MODELADO"/>
+    <tableColumn id="23" name="ENCARGO_TRIBUTARIO_COMPARAVEL"/>
+    <tableColumn id="24" name="CLIENTE_B2B_CREDITO_CBS_POTENCIAL"/>
+    <tableColumn id="25" name="CLIENTE_B2B_CREDITO_IBS_POTENCIAL"/>
+    <tableColumn id="26" name="STATUS_RESULTADO"/>
+    <tableColumn id="27" name="VERSAO_REGRA"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_SIMPLES_2027_COMPARACAO" displayName="tbl_SIMPLES_2027_COMPARACAO" ref="A1:H1" headerRowCount="1">
+  <autoFilter ref="A1:H1"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="ID_CENARIO_BASE"/>
+    <tableColumn id="2" name="ID_CENARIO"/>
+    <tableColumn id="3" name="METRICA"/>
+    <tableColumn id="4" name="BASELINE"/>
+    <tableColumn id="5" name="ALTERNATIVO"/>
+    <tableColumn id="6" name="DELTA"/>
+    <tableColumn id="7" name="STATUS_BASELINE"/>
+    <tableColumn id="8" name="STATUS_ALTERNATIVO"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_VALIDACOES" displayName="tbl_VALIDACOES" ref="A1:K14" headerRowCount="1">
+  <autoFilter ref="A1:K14"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ETAPA"/>
     <tableColumn id="2" name="OK"/>
@@ -483,9 +553,9 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_PROVENIENCIA" displayName="tbl_PROVENIENCIA" ref="A1:B15" headerRowCount="1">
-  <autoFilter ref="A1:B15"/>
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_PROVENIENCIA" displayName="tbl_PROVENIENCIA" ref="A1:B19" headerRowCount="1">
+  <autoFilter ref="A1:B19"/>
   <tableColumns count="2">
     <tableColumn id="1" name="CHAVE"/>
     <tableColumn id="2" name="VALOR"/>
@@ -1243,7 +1313,7 @@
       <c r="C23" s="2" t="n"/>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>NOTA SOBRE O CENÁRIO-CONTROLE</t>
+          <t>NOTA SOBRE O CENÁRIO</t>
         </is>
       </c>
       <c r="E23" s="2" t="n"/>
@@ -6142,7 +6212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -6570,12 +6640,95 @@
       </c>
       <c r="F22" s="2" t="n"/>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="n"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>HIPÓTESES ANALÍTICAS - NÃO NORMATIVAS</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
+      <c r="E25" s="2" t="n"/>
+      <c r="F25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>ORDEM</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>O_QUE_CONTEM</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>QUANDO_EDITAR</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>NIVEL_DE_CUIDADO</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>ANALISE_PARAM</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>hipóteses de sensibilidade</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>alterar premissas analíticas não normativas</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>alto</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A19:E19"/>
   </mergeCells>
   <hyperlinks>
@@ -6588,6 +6741,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.3" right="0.3" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -7727,6 +7881,63 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>ID_ANALISE</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>CHAVE_PARAM</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>VALOR</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>TIPO_VALOR</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
+          <t>DESCRICAO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"str,int,decimal,bool,date"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7948,7 +8159,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FFC000"/>
@@ -8074,7 +8285,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00FFC000"/>
@@ -8172,14 +8383,268 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="18" max="18"/>
+    <col width="31" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="28" customWidth="1" min="21" max="21"/>
+    <col width="27" customWidth="1" min="22" max="22"/>
+    <col width="31" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="18" customWidth="1" min="26" max="26"/>
+    <col width="14" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>ID_CENARIO</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>REGIME_CONSUMO</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>RECEITA_MES</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>RBT12</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>ALIQUOTA_EFETIVA_SIMPLES</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>DAS_TOTAL</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>DAS_CBS</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>DAS_IBS</t>
+        </is>
+      </c>
+      <c r="I1" s="13" t="inlineStr">
+        <is>
+          <t>DAS_OUTROS</t>
+        </is>
+      </c>
+      <c r="J1" s="13" t="inlineStr">
+        <is>
+          <t>CBS_REGULAR_RATE_FRACTION</t>
+        </is>
+      </c>
+      <c r="K1" s="13" t="inlineStr">
+        <is>
+          <t>CBS_RATE_SOURCE</t>
+        </is>
+      </c>
+      <c r="L1" s="13" t="inlineStr">
+        <is>
+          <t>CBS_DEBITO_REGULAR</t>
+        </is>
+      </c>
+      <c r="M1" s="13" t="inlineStr">
+        <is>
+          <t>CBS_CREDITO_EMPRESA_POTENCIAL</t>
+        </is>
+      </c>
+      <c r="N1" s="13" t="inlineStr">
+        <is>
+          <t>CBS_CREDITO_EMPRESA_MODELADO</t>
+        </is>
+      </c>
+      <c r="O1" s="13" t="inlineStr">
+        <is>
+          <t>CBS_VALOR_LIQUIDO_MODELADO</t>
+        </is>
+      </c>
+      <c r="P1" s="13" t="inlineStr">
+        <is>
+          <t>CBS_SALDO_CREDOR_MODELADO</t>
+        </is>
+      </c>
+      <c r="Q1" s="13" t="inlineStr">
+        <is>
+          <t>IBS_REGULAR_RATE_FRACTION</t>
+        </is>
+      </c>
+      <c r="R1" s="13" t="inlineStr">
+        <is>
+          <t>IBS_DEBITO_REGULAR</t>
+        </is>
+      </c>
+      <c r="S1" s="13" t="inlineStr">
+        <is>
+          <t>IBS_CREDITO_EMPRESA_POTENCIAL</t>
+        </is>
+      </c>
+      <c r="T1" s="13" t="inlineStr">
+        <is>
+          <t>IBS_CREDITO_EMPRESA_MODELADO</t>
+        </is>
+      </c>
+      <c r="U1" s="13" t="inlineStr">
+        <is>
+          <t>IBS_VALOR_LIQUIDO_MODELADO</t>
+        </is>
+      </c>
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>IBS_SALDO_CREDOR_MODELADO</t>
+        </is>
+      </c>
+      <c r="W1" s="13" t="inlineStr">
+        <is>
+          <t>ENCARGO_TRIBUTARIO_COMPARAVEL</t>
+        </is>
+      </c>
+      <c r="X1" s="13" t="inlineStr">
+        <is>
+          <t>CLIENTE_B2B_CREDITO_CBS_POTENCIAL</t>
+        </is>
+      </c>
+      <c r="Y1" s="13" t="inlineStr">
+        <is>
+          <t>CLIENTE_B2B_CREDITO_IBS_POTENCIAL</t>
+        </is>
+      </c>
+      <c r="Z1" s="13" t="inlineStr">
+        <is>
+          <t>STATUS_RESULTADO</t>
+        </is>
+      </c>
+      <c r="AA1" s="13" t="inlineStr">
+        <is>
+          <t>VERSAO_REGRA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="inlineStr">
+        <is>
+          <t>ID_CENARIO_BASE</t>
+        </is>
+      </c>
+      <c r="B1" s="13" t="inlineStr">
+        <is>
+          <t>ID_CENARIO</t>
+        </is>
+      </c>
+      <c r="C1" s="13" t="inlineStr">
+        <is>
+          <t>METRICA</t>
+        </is>
+      </c>
+      <c r="D1" s="13" t="inlineStr">
+        <is>
+          <t>BASELINE</t>
+        </is>
+      </c>
+      <c r="E1" s="13" t="inlineStr">
+        <is>
+          <t>ALTERNATIVO</t>
+        </is>
+      </c>
+      <c r="F1" s="13" t="inlineStr">
+        <is>
+          <t>DELTA</t>
+        </is>
+      </c>
+      <c r="G1" s="13" t="inlineStr">
+        <is>
+          <t>STATUS_BASELINE</t>
+        </is>
+      </c>
+      <c r="H1" s="13" t="inlineStr">
+        <is>
+          <t>STATUS_ALTERNATIVO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8375,7 +8840,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CONTEXTO_TRIBUTARIO</t>
+          <t>ANALISE_PARAM</t>
         </is>
       </c>
       <c r="B10" t="b">
@@ -8390,7 +8855,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LANCAMENTOS_PARTIDAS</t>
+          <t>CONTEXTO_TRIBUTARIO</t>
         </is>
       </c>
       <c r="B11" t="b">
@@ -8405,7 +8870,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RAZAO_BALANCETE</t>
+          <t>LANCAMENTOS_PARTIDAS</t>
         </is>
       </c>
       <c r="B12" t="b">
@@ -8420,13 +8885,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DEMONSTRACOES</t>
+          <t>RAZAO_BALANCETE</t>
         </is>
       </c>
       <c r="B13" t="b">
         <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DEMONSTRACOES</t>
+        </is>
+      </c>
+      <c r="B14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
         <is>
           <t>ok</t>
         </is>
@@ -8440,14 +8920,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008064A2"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8474,7 +8954,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>spec_11_excel_workbook_v1</t>
+          <t>spec_12_excel_workbook_v1</t>
         </is>
       </c>
     </row>
@@ -8517,118 +8997,156 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>simulation_id</t>
+          <t>simples_2027_rule_spec_version</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CANONICAL_CBS_2026</t>
+          <t>spec_12_simples_2027_puro_hibrido_v1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>scenario_name</t>
+          <t>simulation_id</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>cbs_2026_counterfactual_control</t>
+          <t>CANONICAL_CBS_2026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>simulation_spec_version</t>
+          <t>scenario_name</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>spec_11_excel_workbook_v1</t>
+          <t>cbs_2026_counterfactual_control</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>posting_rule_version</t>
+          <t>simulation_spec_version</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>posting_rules_v1</t>
+          <t>spec_12_excel_workbook_v1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>statement_mapping_source</t>
+          <t>posting_rule_version</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MAPEAMENTO_DF</t>
+          <t>posting_rules_v1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tax_context_configured</t>
+          <t>statement_mapping_source</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRUE</t>
+          <t>MAPEAMENTO_DF</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>tax_normative_versions</t>
+          <t>tax_context_configured</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CBS_2026_08_31_V1</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>tax_normative_versions</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BRL</t>
+          <t>CBS_2026_08_31_V1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>chart_source</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>template_or_input_PLANO_CONTAS</t>
+          <t>analysis_id</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>analysis_parameters_present</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cbs_rate_source</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BRL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>chart_source</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>template_or_input_PLANO_CONTAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>event_spec_versions</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>spec_03_events_v1</t>
         </is>
@@ -8973,7 +9491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8995,7 +9513,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>spec_11_excel_workbook_v1</t>
+          <t>spec_12_excel_workbook_v1</t>
         </is>
       </c>
     </row>
@@ -9031,7 +9549,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONFIG, ENTIDADE, PLANO_CONTAS, MAPEAMENTO_CONTAS, EVENTOS, EVENTOS_FISCAIS, MAPEAMENTO_DF, CENARIOS_TRIBUTARIOS e FISCAL_PARAM.</t>
+          <t>CONFIG, ENTIDADE, PLANO_CONTAS, MAPEAMENTO_CONTAS, EVENTOS, EVENTOS_FISCAIS, MAPEAMENTO_DF, CENARIOS_TRIBUTARIOS, FISCAL_PARAM e ANALISE_PARAM.</t>
         </is>
       </c>
     </row>
@@ -9055,29 +9573,53 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spec 08 materializa a interface tributária; Spec 09 calcula CBS 2026; Spec 10 executa múltiplos cenários; Spec 11 compara e materializa saídas fiscais derivadas.</t>
+          <t>Spec 08 materializa a interface tributária; Spec 09 calcula CBS 2026; Spec 10 executa múltiplos cenários; Spec 11 compara e materializa saídas fiscais derivadas; Spec 12 compara Simples 2027 puro e híbrido.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Derivadas</t>
+          <t>FISCAL_PARAM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LANCAMENTOS, PARTIDAS, VINCULO_EVENTO_LCTO, DIARIO, RAZAO, BALANCETE, BP, DRE, FISCAL_RESULTADOS_OPERACAO, FISCAL_APURACAO, COMPARATIVO_CENARIOS, VALIDACOES e PROVENIENCIA.</t>
+          <t>Fonte normativa parametrizada com proveniência.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>ANALISE_PARAM</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Hipóteses declaradas para análise de sensibilidade; uma hipótese nunca é apresentada como legislação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Derivadas</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LANCAMENTOS, PARTIDAS, VINCULO_EVENTO_LCTO, DIARIO, RAZAO, BALANCETE, BP, DRE, FISCAL_RESULTADOS_OPERACAO, FISCAL_APURACAO, COMPARATIVO_CENARIOS, SIMPLES_2027_RESULTADOS, SIMPLES_2027_COMPARACAO, VALIDACOES e PROVENIENCIA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Fonte de verdade</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Objetos derivados são reconstruídos a partir das abas de entrada.</t>
         </is>
@@ -9188,7 +9730,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>spec_11_excel_workbook_v1</t>
+          <t>spec_12_excel_workbook_v1</t>
         </is>
       </c>
     </row>

--- a/artifacts/contabilidade_parametrizada.xlsx
+++ b/artifacts/contabilidade_parametrizada.xlsx
@@ -401,21 +401,7 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_ANALISE_PARAM" displayName="tbl_ANALISE_PARAM" ref="A1:E1" headerRowCount="1">
-  <autoFilter ref="A1:E1"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="ID_ANALISE"/>
-    <tableColumn id="2" name="CHAVE_PARAM"/>
-    <tableColumn id="3" name="VALOR"/>
-    <tableColumn id="4" name="TIPO_VALOR"/>
-    <tableColumn id="5" name="DESCRICAO"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_FISCAL_RESULTADOS_OPERACAO" displayName="tbl_FISCAL_RESULTADOS_OPERACAO" ref="A1:I5" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="tbl_FISCAL_RESULTADOS_OPERACAO" displayName="tbl_FISCAL_RESULTADOS_OPERACAO" ref="A1:I5" headerRowCount="1">
   <autoFilter ref="A1:I5"/>
   <tableColumns count="9">
     <tableColumn id="1" name="ID_CENARIO"/>
@@ -427,6 +413,23 @@
     <tableColumn id="7" name="CREDITO"/>
     <tableColumn id="8" name="DEBITO"/>
     <tableColumn id="9" name="VERSAO_REGRA"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_FISCAL_APURACAO" displayName="tbl_FISCAL_APURACAO" ref="A1:H3" headerRowCount="1">
+  <autoFilter ref="A1:H3"/>
+  <tableColumns count="8">
+    <tableColumn id="1" name="ID_CENARIO"/>
+    <tableColumn id="2" name="TRIBUTO"/>
+    <tableColumn id="3" name="S_APUR"/>
+    <tableColumn id="4" name="T_RECOLHER"/>
+    <tableColumn id="5" name="P_CASH"/>
+    <tableColumn id="6" name="E_DRE"/>
+    <tableColumn id="7" name="C_SALDO"/>
+    <tableColumn id="8" name="VERSAO_REGRA"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -447,24 +450,7 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_FISCAL_APURACAO" displayName="tbl_FISCAL_APURACAO" ref="A1:H3" headerRowCount="1">
-  <autoFilter ref="A1:H3"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="ID_CENARIO"/>
-    <tableColumn id="2" name="TRIBUTO"/>
-    <tableColumn id="3" name="S_APUR"/>
-    <tableColumn id="4" name="T_RECOLHER"/>
-    <tableColumn id="5" name="P_CASH"/>
-    <tableColumn id="6" name="E_DRE"/>
-    <tableColumn id="7" name="C_SALDO"/>
-    <tableColumn id="8" name="VERSAO_REGRA"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_COMPARATIVO_CENARIOS" displayName="tbl_COMPARATIVO_CENARIOS" ref="A1:H2" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_COMPARATIVO_CENARIOS" displayName="tbl_COMPARATIVO_CENARIOS" ref="A1:H2" headerRowCount="1">
   <autoFilter ref="A1:H2"/>
   <tableColumns count="8">
     <tableColumn id="1" name="ID_CENARIO_BASE"/>
@@ -480,61 +466,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_SIMPLES_2027_RESULTADOS" displayName="tbl_SIMPLES_2027_RESULTADOS" ref="A1:AA1" headerRowCount="1">
-  <autoFilter ref="A1:AA1"/>
-  <tableColumns count="27">
-    <tableColumn id="1" name="ID_CENARIO"/>
-    <tableColumn id="2" name="REGIME_CONSUMO"/>
-    <tableColumn id="3" name="RECEITA_MES"/>
-    <tableColumn id="4" name="RBT12"/>
-    <tableColumn id="5" name="ALIQUOTA_EFETIVA_SIMPLES"/>
-    <tableColumn id="6" name="DAS_TOTAL"/>
-    <tableColumn id="7" name="DAS_CBS"/>
-    <tableColumn id="8" name="DAS_IBS"/>
-    <tableColumn id="9" name="DAS_OUTROS"/>
-    <tableColumn id="10" name="CBS_REGULAR_RATE_FRACTION"/>
-    <tableColumn id="11" name="CBS_RATE_SOURCE"/>
-    <tableColumn id="12" name="CBS_DEBITO_REGULAR"/>
-    <tableColumn id="13" name="CBS_CREDITO_EMPRESA_POTENCIAL"/>
-    <tableColumn id="14" name="CBS_CREDITO_EMPRESA_MODELADO"/>
-    <tableColumn id="15" name="CBS_VALOR_LIQUIDO_MODELADO"/>
-    <tableColumn id="16" name="CBS_SALDO_CREDOR_MODELADO"/>
-    <tableColumn id="17" name="IBS_REGULAR_RATE_FRACTION"/>
-    <tableColumn id="18" name="IBS_DEBITO_REGULAR"/>
-    <tableColumn id="19" name="IBS_CREDITO_EMPRESA_POTENCIAL"/>
-    <tableColumn id="20" name="IBS_CREDITO_EMPRESA_MODELADO"/>
-    <tableColumn id="21" name="IBS_VALOR_LIQUIDO_MODELADO"/>
-    <tableColumn id="22" name="IBS_SALDO_CREDOR_MODELADO"/>
-    <tableColumn id="23" name="ENCARGO_TRIBUTARIO_COMPARAVEL"/>
-    <tableColumn id="24" name="CLIENTE_B2B_CREDITO_CBS_POTENCIAL"/>
-    <tableColumn id="25" name="CLIENTE_B2B_CREDITO_IBS_POTENCIAL"/>
-    <tableColumn id="26" name="STATUS_RESULTADO"/>
-    <tableColumn id="27" name="VERSAO_REGRA"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_SIMPLES_2027_COMPARACAO" displayName="tbl_SIMPLES_2027_COMPARACAO" ref="A1:H1" headerRowCount="1">
-  <autoFilter ref="A1:H1"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="ID_CENARIO_BASE"/>
-    <tableColumn id="2" name="ID_CENARIO"/>
-    <tableColumn id="3" name="METRICA"/>
-    <tableColumn id="4" name="BASELINE"/>
-    <tableColumn id="5" name="ALTERNATIVO"/>
-    <tableColumn id="6" name="DELTA"/>
-    <tableColumn id="7" name="STATUS_BASELINE"/>
-    <tableColumn id="8" name="STATUS_ALTERNATIVO"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_VALIDACOES" displayName="tbl_VALIDACOES" ref="A1:K14" headerRowCount="1">
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_VALIDACOES" displayName="tbl_VALIDACOES" ref="A1:K14" headerRowCount="1">
   <autoFilter ref="A1:K14"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ETAPA"/>
@@ -553,8 +486,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_PROVENIENCIA" displayName="tbl_PROVENIENCIA" ref="A1:B19" headerRowCount="1">
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_PROVENIENCIA" displayName="tbl_PROVENIENCIA" ref="A1:B19" headerRowCount="1">
   <autoFilter ref="A1:B19"/>
   <tableColumns count="2">
     <tableColumn id="1" name="CHAVE"/>
@@ -7929,9 +7862,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -8561,9 +8491,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -8631,9 +8558,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
